--- a/ControlTable_Sentry_ARL/ControlTable_SentryARL.xlsx
+++ b/ControlTable_Sentry_ARL/ControlTable_SentryARL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Y26\ControlTable_Sentry_ARL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8297EE-F942-47C0-8B6E-AB5534A2B99B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3311668A-E375-48E2-ADB6-AE27F8110E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1431B911-F057-4304-9798-EC2268DBF203}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="494">
   <si>
     <t>项目</t>
     <phoneticPr fontId="0" type="noConversion"/>
@@ -2055,6 +2055,195 @@
   </si>
   <si>
     <t>not have CALL D:\FA_PRO\LCD\LCDLight\AutoLCDLightCapture.bat</t>
+  </si>
+  <si>
+    <t>Program have n't add label createAP_Xml &amp; APSSID Line A1  Wrong
+HP不在A1生产</t>
+  </si>
+  <si>
+    <t>Close : D:\FA_PRO\BaseXML\TS_Update\TS_Update.bat</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>Not Add先不加</t>
+  </si>
+  <si>
+    <t>Close
+101BFAI</t>
+  </si>
+  <si>
+    <t>Not Update
+不在A1生产
+不带HDMI</t>
+  </si>
+  <si>
+    <t>Not Update</t>
+  </si>
+  <si>
+    <t>Not Need</t>
+  </si>
+  <si>
+    <t>Close有专门的风扇异音箱</t>
+  </si>
+  <si>
+    <t>Close  NO issue</t>
+  </si>
+  <si>
+    <t>Close ( skip checkSum)</t>
+  </si>
+  <si>
+    <t>Close 无此issue</t>
+  </si>
+  <si>
+    <t>- Not have test fingerprint, IR camera
+-Turn off all led only turn on led camera</t>
+  </si>
+  <si>
+    <t>- Turn on led caps, keyF4,button_power
+- Take a picture LCD 0 light
+- XML add Led 3: 
++ take a picture LCD 100 light
++ turn on kbbl,change status_led_button_power</t>
+  </si>
+  <si>
+    <t>回和X都测</t>
+  </si>
+  <si>
+    <t>Program not call D:\SFCS\SFCS_Log_Stage.bat</t>
+  </si>
+  <si>
+    <t>NOT NEED</t>
+  </si>
+  <si>
+    <t>NOT HAVE</t>
+  </si>
+  <si>
+    <t>IF @%MODELFAMILY%==@4PD0WR010001 GOTO pass
+IF @%MODELFAMILY%==@4PD0WR01A001 GOTO pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLOSE </t>
+  </si>
+  <si>
+    <t>CLOSE</t>
+  </si>
+  <si>
+    <t>NOT TEST</t>
+  </si>
+  <si>
+    <t>check</t>
+  </si>
+  <si>
+    <t>Onbroad by pass</t>
+  </si>
+  <si>
+    <t>- Not remove Items pass 
+- Not Cover No Wlan</t>
+  </si>
+  <si>
+    <t>-Program Not call D:\SFCS\SFCS_Log_Stage.bat 
+- But connect wifi get log SVC</t>
+  </si>
+  <si>
+    <t>Program test old (only 2 color)</t>
+  </si>
+  <si>
+    <t>location TU</t>
+  </si>
+  <si>
+    <t>TEST 100 %</t>
+  </si>
+  <si>
+    <t>NOT HAVE ( XML not test auto)</t>
+  </si>
+  <si>
+    <t>NOT HAVE ( XML not test auto)百百WDL手测</t>
+  </si>
+  <si>
+    <t>D:\BURNIN\Link\Link_net.bat</t>
+  </si>
+  <si>
+    <t>TO_Update.py</t>
+  </si>
+  <si>
+    <t>CLOSE  -_WCD</t>
+  </si>
+  <si>
+    <t>D:\BURNIN\SAFE\SAFE64.BAT</t>
+  </si>
+  <si>
+    <t>测试xml有</t>
+  </si>
+  <si>
+    <t>NOT HAVE
+不带AX211</t>
+  </si>
+  <si>
+    <t>在TV</t>
+  </si>
+  <si>
+    <t>D:\BURNIN\SAFE\SAFE64.BAT ( need file .py)</t>
+  </si>
+  <si>
+    <t>CLOSE ( cycle =2)</t>
+  </si>
+  <si>
+    <t>BY PASS ( BIOS đã tự setmodelname ?)</t>
+  </si>
+  <si>
+    <t>CLOSE
+Program upload_mac WLANMAC, BTMAC
+BMAC have D:\BURNIN\Upload_MAC\Upload_BMAC.BAT</t>
+  </si>
+  <si>
+    <t>??</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT HAVE  不带GPU </t>
+  </si>
+  <si>
+    <t>Link_net..bat</t>
+  </si>
+  <si>
+    <t>BY PASS</t>
+  </si>
+  <si>
+    <t>CLOSE ( TO_Update.py .py)</t>
+  </si>
+  <si>
+    <t>NOT USE</t>
+  </si>
+  <si>
+    <t>Not ADD_ Copy Wim &amp; FICore</t>
+  </si>
+  <si>
+    <t>CLOSE ( CYCLE=20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wrong status --&gt; Just sleep, can't join in S0 status </t>
+  </si>
+  <si>
+    <t>CLOSE (cycle =20)</t>
+  </si>
+  <si>
+    <t>Only upload_Bmac beacause not Phycical LAN</t>
+  </si>
+  <si>
+    <t>By PASS</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>Goto pass line A4,A5</t>
+  </si>
+  <si>
+    <t>no have</t>
+  </si>
+  <si>
+    <t>IF @%TECHECK%==@NOTREADY GOTO PASS</t>
   </si>
 </sst>
 </file>
@@ -2380,7 +2569,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2431,9 +2620,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2445,9 +2631,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2470,7 +2653,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2549,6 +2731,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2886,18 +3074,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30EB096E-FFC3-4F89-8A88-7E61B5D121F9}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:I310"/>
+  <dimension ref="A1:I311"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.7265625" style="54" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.26953125" style="54" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.81640625" style="55" customWidth="1"/>
-    <col min="4" max="4" width="81.26953125" style="56" customWidth="1"/>
-    <col min="5" max="5" width="51.453125" style="57" customWidth="1"/>
+    <col min="1" max="1" width="16.7265625" style="51" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.26953125" style="51" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.81640625" style="52" customWidth="1"/>
+    <col min="4" max="4" width="81.26953125" style="53" customWidth="1"/>
+    <col min="5" max="5" width="51.453125" style="54" customWidth="1"/>
     <col min="6" max="6" width="23.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2913,9 +3101,12 @@
       <c r="E1" s="4" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="59" t="s">
+      <c r="F1" s="58" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="56" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="5">
@@ -2928,8 +3119,8 @@
       <c r="D2" s="7"/>
       <c r="E2" s="8"/>
     </row>
-    <row r="3" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="59"/>
+    <row r="3" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="56"/>
       <c r="B3" s="5">
         <f t="shared" ref="B3:B13" si="0">ROW()-1</f>
         <v>2</v>
@@ -2940,8 +3131,8 @@
       <c r="D3" s="9"/>
       <c r="E3" s="8"/>
     </row>
-    <row r="4" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="59"/>
+    <row r="4" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="56"/>
       <c r="B4" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2952,8 +3143,8 @@
       <c r="D4" s="9"/>
       <c r="E4" s="8"/>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="59"/>
+    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="56"/>
       <c r="B5" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2966,8 +3157,8 @@
       </c>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="59"/>
+    <row r="6" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="56"/>
       <c r="B6" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2980,8 +3171,8 @@
       </c>
       <c r="E6" s="8"/>
     </row>
-    <row r="7" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="59" t="s">
+    <row r="7" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="56" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="5">
@@ -2996,8 +3187,8 @@
       </c>
       <c r="E7" s="8"/>
     </row>
-    <row r="8" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="59"/>
+    <row r="8" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="56"/>
       <c r="B8" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -3010,8 +3201,8 @@
       </c>
       <c r="E8" s="8"/>
     </row>
-    <row r="9" spans="1:5" ht="58" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="59"/>
+    <row r="9" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="56"/>
       <c r="B9" s="5">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -3024,8 +3215,8 @@
       </c>
       <c r="E9" s="8"/>
     </row>
-    <row r="10" spans="1:5" ht="58" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="59"/>
+    <row r="10" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="56"/>
       <c r="B10" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -3038,8 +3229,8 @@
       </c>
       <c r="E10" s="8"/>
     </row>
-    <row r="11" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="59"/>
+    <row r="11" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="56"/>
       <c r="B11" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -3052,8 +3243,8 @@
       </c>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" spans="1:5" ht="58" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="59"/>
+    <row r="12" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="56"/>
       <c r="B12" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -3066,8 +3257,8 @@
       </c>
       <c r="E12" s="8"/>
     </row>
-    <row r="13" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="59"/>
+    <row r="13" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="56"/>
       <c r="B13" s="5">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -3080,7 +3271,7 @@
       </c>
       <c r="E13" s="8"/>
     </row>
-    <row r="14" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10" t="s">
         <v>27</v>
       </c>
@@ -3095,7 +3286,7 @@
       </c>
       <c r="E14" s="8"/>
     </row>
-    <row r="15" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="10" t="s">
         <v>27</v>
       </c>
@@ -3110,7 +3301,7 @@
       </c>
       <c r="E15" s="8"/>
     </row>
-    <row r="16" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10" t="s">
         <v>27</v>
       </c>
@@ -3363,7 +3554,7 @@
       </c>
       <c r="E32" s="8"/>
     </row>
-    <row r="33" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10" t="s">
         <v>27</v>
       </c>
@@ -3378,7 +3569,7 @@
       </c>
       <c r="E33" s="8"/>
     </row>
-    <row r="34" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10" t="s">
         <v>27</v>
       </c>
@@ -3393,7 +3584,7 @@
       </c>
       <c r="E34" s="8"/>
     </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10" t="s">
         <v>27</v>
       </c>
@@ -3408,7 +3599,7 @@
       </c>
       <c r="E35" s="8"/>
     </row>
-    <row r="36" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="10" t="s">
         <v>27</v>
       </c>
@@ -3423,7 +3614,7 @@
       </c>
       <c r="E36" s="8"/>
     </row>
-    <row r="37" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10" t="s">
         <v>27</v>
       </c>
@@ -3438,7 +3629,7 @@
       </c>
       <c r="E37" s="8"/>
     </row>
-    <row r="38" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10" t="s">
         <v>27</v>
       </c>
@@ -3453,7 +3644,7 @@
       </c>
       <c r="E38" s="8"/>
     </row>
-    <row r="39" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="10" t="s">
         <v>27</v>
       </c>
@@ -3468,7 +3659,7 @@
       </c>
       <c r="E39" s="8"/>
     </row>
-    <row r="40" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="10" t="s">
         <v>27</v>
       </c>
@@ -3483,7 +3674,7 @@
       </c>
       <c r="E40" s="8"/>
     </row>
-    <row r="41" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="10" t="s">
         <v>27</v>
       </c>
@@ -3498,7 +3689,7 @@
       </c>
       <c r="E41" s="8"/>
     </row>
-    <row r="42" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10" t="s">
         <v>27</v>
       </c>
@@ -3513,7 +3704,7 @@
       </c>
       <c r="E42" s="8"/>
     </row>
-    <row r="43" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10" t="s">
         <v>27</v>
       </c>
@@ -3528,7 +3719,7 @@
       </c>
       <c r="E43" s="8"/>
     </row>
-    <row r="44" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="10" t="s">
         <v>27</v>
       </c>
@@ -3541,7 +3732,7 @@
       <c r="D44" s="9"/>
       <c r="E44" s="8"/>
     </row>
-    <row r="45" spans="1:5" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="10" t="s">
         <v>27</v>
       </c>
@@ -3556,7 +3747,7 @@
       </c>
       <c r="E45" s="8"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="11" t="s">
         <v>89</v>
       </c>
@@ -3572,8 +3763,11 @@
       <c r="E46" s="12" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="F46" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="11" t="s">
         <v>89</v>
       </c>
@@ -3589,8 +3783,11 @@
       <c r="E47" s="12" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F47" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="11" t="s">
         <v>89</v>
       </c>
@@ -3604,6 +3801,7 @@
         <v>96</v>
       </c>
       <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
     </row>
     <row r="49" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" s="11" t="s">
@@ -3621,6 +3819,9 @@
       <c r="E49" s="14" t="s">
         <v>172</v>
       </c>
+      <c r="F49" s="14" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="11" t="s">
@@ -3638,6 +3839,9 @@
       <c r="E50" s="15" t="s">
         <v>172</v>
       </c>
+      <c r="F50" s="15" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="51" spans="1:6" ht="291.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="11" t="s">
@@ -3655,7 +3859,9 @@
       <c r="E51" s="17" t="s">
         <v>428</v>
       </c>
-      <c r="F51" s="18"/>
+      <c r="F51" s="17" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="52" spans="1:6" ht="87" x14ac:dyDescent="0.35">
       <c r="A52" s="11" t="s">
@@ -3672,6 +3878,9 @@
       </c>
       <c r="E52" s="12" t="s">
         <v>422</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
@@ -3688,6 +3897,9 @@
       <c r="E53" s="13" t="s">
         <v>423</v>
       </c>
+      <c r="F53" s="13" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="54" spans="1:6" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A54" s="11" t="s">
@@ -3705,7 +3917,9 @@
       <c r="E54" s="13" t="s">
         <v>423</v>
       </c>
-      <c r="F54" s="18"/>
+      <c r="F54" s="18" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="55" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A55" s="11" t="s">
@@ -3723,6 +3937,9 @@
       <c r="E55" s="12" t="s">
         <v>92</v>
       </c>
+      <c r="F55" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="11" t="s">
@@ -3740,6 +3957,9 @@
       <c r="E56" s="12" t="s">
         <v>92</v>
       </c>
+      <c r="F56" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="57" spans="1:6" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A57" s="11" t="s">
@@ -3757,6 +3977,9 @@
       <c r="E57" s="12" t="s">
         <v>92</v>
       </c>
+      <c r="F57" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="11" t="s">
@@ -3769,8 +3992,11 @@
         <v>113</v>
       </c>
       <c r="D58" s="9"/>
-      <c r="E58" s="58" t="s">
+      <c r="E58" s="55" t="s">
         <v>423</v>
+      </c>
+      <c r="F58" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="113.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -3786,8 +4012,11 @@
       <c r="D59" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E59" s="58" t="s">
+      <c r="E59" s="55" t="s">
         <v>424</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="174" x14ac:dyDescent="0.35">
@@ -3800,13 +4029,15 @@
       <c r="C60" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="D60" s="20" t="s">
+      <c r="D60" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="E60" s="21" t="s">
+      <c r="E60" s="20" t="s">
         <v>423</v>
       </c>
-      <c r="F60" s="19"/>
+      <c r="F60" s="20" t="s">
+        <v>441</v>
+      </c>
     </row>
     <row r="61" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A61" s="11" t="s">
@@ -3815,16 +4046,18 @@
       <c r="B61" s="5">
         <v>16</v>
       </c>
-      <c r="C61" s="22" t="s">
+      <c r="C61" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="D61" s="20" t="s">
+      <c r="D61" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="E61" s="21" t="s">
+      <c r="E61" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="F61" s="23"/>
+      <c r="F61" s="20" t="s">
+        <v>442</v>
+      </c>
     </row>
     <row r="62" spans="1:6" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="11" t="s">
@@ -3841,6 +4074,9 @@
       </c>
       <c r="E62" s="9" t="s">
         <v>426</v>
+      </c>
+      <c r="F62" s="57" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
@@ -3857,6 +4093,9 @@
       <c r="E63" s="15" t="s">
         <v>172</v>
       </c>
+      <c r="F63" s="15" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="11" t="s">
@@ -3872,6 +4111,9 @@
       <c r="E64" s="12" t="s">
         <v>429</v>
       </c>
+      <c r="F64" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="11" t="s">
@@ -3887,6 +4129,9 @@
       <c r="E65" s="15" t="s">
         <v>172</v>
       </c>
+      <c r="F65" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="11" t="s">
@@ -3902,6 +4147,9 @@
       <c r="E66" s="12" t="s">
         <v>92</v>
       </c>
+      <c r="F66" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="67" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A67" s="11" t="s">
@@ -3915,6 +4163,9 @@
       </c>
       <c r="D67" s="9"/>
       <c r="E67" s="12"/>
+      <c r="F67" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="11" t="s">
@@ -3928,6 +4179,9 @@
       </c>
       <c r="D68" s="9"/>
       <c r="E68" s="12"/>
+      <c r="F68" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="11" t="s">
@@ -3941,6 +4195,9 @@
       </c>
       <c r="D69" s="9"/>
       <c r="E69" s="12"/>
+      <c r="F69" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="70" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A70" s="11" t="s">
@@ -3958,7 +4215,9 @@
       <c r="E70" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="F70" s="17"/>
+      <c r="F70" s="12" t="s">
+        <v>444</v>
+      </c>
     </row>
     <row r="71" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A71" s="11" t="s">
@@ -3976,6 +4235,9 @@
       <c r="E71" s="12" t="s">
         <v>172</v>
       </c>
+      <c r="F71" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="72" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A72" s="11" t="s">
@@ -3987,12 +4249,15 @@
       <c r="C72" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="D72" s="24" t="s">
+      <c r="D72" s="22" t="s">
         <v>133</v>
       </c>
       <c r="E72" s="12" t="s">
         <v>427</v>
       </c>
+      <c r="F72" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="73" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="11" t="s">
@@ -4010,6 +4275,9 @@
       <c r="E73" s="12" t="s">
         <v>172</v>
       </c>
+      <c r="F73" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="11" t="s">
@@ -4025,6 +4293,9 @@
         <v>100</v>
       </c>
       <c r="E74" s="12"/>
+      <c r="F74" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="11" t="s">
@@ -4042,6 +4313,9 @@
       <c r="E75" s="12" t="s">
         <v>430</v>
       </c>
+      <c r="F75" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="76" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A76" s="11" t="s">
@@ -4056,8 +4330,11 @@
       <c r="D76" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E76" s="19" t="s">
+      <c r="E76" s="18" t="s">
         <v>432</v>
+      </c>
+      <c r="F76" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
@@ -4073,8 +4350,11 @@
       <c r="D77" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="E77" s="19" t="s">
+      <c r="E77" s="18" t="s">
         <v>431</v>
+      </c>
+      <c r="F77" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
@@ -4093,6 +4373,9 @@
       <c r="E78" s="12" t="s">
         <v>172</v>
       </c>
+      <c r="F78" s="12" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="11" t="s">
@@ -4110,6 +4393,9 @@
       <c r="E79" s="12" t="s">
         <v>172</v>
       </c>
+      <c r="F79" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="80" spans="1:6" ht="255" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="11" t="s">
@@ -4124,11 +4410,14 @@
       <c r="D80" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="E80" s="19" t="s">
+      <c r="E80" s="18" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" ht="111" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F80" s="12" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="111" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="11" t="s">
         <v>89</v>
       </c>
@@ -4144,23 +4433,29 @@
       <c r="E81" s="12" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" ht="26" x14ac:dyDescent="0.35">
+      <c r="F81" s="12" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="26" x14ac:dyDescent="0.35">
       <c r="A82" s="11" t="s">
         <v>89</v>
       </c>
       <c r="B82" s="5">
         <v>37</v>
       </c>
-      <c r="C82" s="25" t="s">
+      <c r="C82" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="D82" s="26" t="s">
+      <c r="D82" s="24" t="s">
         <v>148</v>
       </c>
       <c r="E82" s="12"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F82" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="11" t="s">
         <v>89</v>
       </c>
@@ -4176,8 +4471,11 @@
       <c r="E83" s="12" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" ht="133.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F83" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="133.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="11" t="s">
         <v>89</v>
       </c>
@@ -4193,8 +4491,11 @@
       <c r="E84" s="12" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" ht="288" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F84" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="288" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="11" t="s">
         <v>89</v>
       </c>
@@ -4207,11 +4508,14 @@
       <c r="D85" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="E85" s="19" t="s">
+      <c r="E85" s="18" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="F85" s="18" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="116" x14ac:dyDescent="0.35">
       <c r="A86" s="11" t="s">
         <v>89</v>
       </c>
@@ -4224,11 +4528,14 @@
       <c r="D86" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="E86" s="29" t="s">
+      <c r="E86" s="27" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="F86" s="18" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A87" s="11" t="s">
         <v>89</v>
       </c>
@@ -4241,9 +4548,14 @@
       <c r="D87" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="E87" s="13"/>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E87" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="F87" s="13" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="11" t="s">
         <v>89</v>
       </c>
@@ -4256,9 +4568,14 @@
       <c r="D88" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E88" s="12"/>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E88" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="F88" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="11" t="s">
         <v>89</v>
       </c>
@@ -4271,9 +4588,14 @@
       <c r="D89" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="E89" s="12"/>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E89" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="F89" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="11" t="s">
         <v>89</v>
       </c>
@@ -4286,9 +4608,14 @@
       <c r="D90" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="E90" s="12"/>
-    </row>
-    <row r="91" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="E90" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="F90" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A91" s="11" t="s">
         <v>89</v>
       </c>
@@ -4301,9 +4628,14 @@
       <c r="D91" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="E91" s="12"/>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E91" s="18" t="s">
+        <v>491</v>
+      </c>
+      <c r="F91" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="11" t="s">
         <v>89</v>
       </c>
@@ -4316,9 +4648,12 @@
       <c r="D92" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E92" s="13"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E92" s="18" t="s">
+        <v>492</v>
+      </c>
+      <c r="F92" s="13"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="11" t="s">
         <v>89</v>
       </c>
@@ -4331,9 +4666,14 @@
       <c r="D93" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E93" s="12"/>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E93" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="F93" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="11" t="s">
         <v>89</v>
       </c>
@@ -4346,9 +4686,12 @@
       <c r="D94" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E94" s="13"/>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E94" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="F94" s="13"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="11" t="s">
         <v>89</v>
       </c>
@@ -4361,9 +4704,12 @@
       <c r="D95" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E95" s="13"/>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E95" s="13" t="s">
+        <v>492</v>
+      </c>
+      <c r="F95" s="13"/>
+    </row>
+    <row r="96" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A96" s="11" t="s">
         <v>89</v>
       </c>
@@ -4376,7 +4722,12 @@
       <c r="D96" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="E96" s="19"/>
+      <c r="E96" s="18" t="s">
+        <v>493</v>
+      </c>
+      <c r="F96" s="18" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="97" spans="1:9" ht="58" x14ac:dyDescent="0.35">
       <c r="A97" s="11" t="s">
@@ -4392,7 +4743,10 @@
         <v>171</v>
       </c>
       <c r="E97" s="13"/>
-      <c r="I97" s="27" t="s">
+      <c r="F97" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="I97" s="25" t="s">
         <v>173</v>
       </c>
     </row>
@@ -4409,7 +4763,10 @@
       <c r="D98" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="E98" s="28"/>
+      <c r="E98" s="26"/>
+      <c r="F98" s="26" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" s="11" t="s">
@@ -4424,7 +4781,10 @@
       <c r="D99" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E99" s="28"/>
+      <c r="E99" s="26"/>
+      <c r="F99" s="26" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="100" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A100" s="11" t="s">
@@ -4439,7 +4799,10 @@
       <c r="D100" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="E100" s="29"/>
+      <c r="E100" s="27"/>
+      <c r="F100" s="27" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" s="11" t="s">
@@ -4454,7 +4817,10 @@
       <c r="D101" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E101" s="29"/>
+      <c r="E101" s="27"/>
+      <c r="F101" s="27" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" s="11" t="s">
@@ -4469,7 +4835,10 @@
       <c r="D102" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E102" s="28"/>
+      <c r="E102" s="26"/>
+      <c r="F102" s="26" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" s="11" t="s">
@@ -4484,7 +4853,10 @@
       <c r="D103" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E103" s="29"/>
+      <c r="E103" s="27"/>
+      <c r="F103" s="27" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" s="11" t="s">
@@ -4499,7 +4871,10 @@
       <c r="D104" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E104" s="29"/>
+      <c r="E104" s="27"/>
+      <c r="F104" s="27" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" s="11" t="s">
@@ -4514,7 +4889,10 @@
       <c r="D105" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E105" s="29"/>
+      <c r="E105" s="27"/>
+      <c r="F105" s="27" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" s="11" t="s">
@@ -4529,7 +4907,10 @@
       <c r="D106" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E106" s="29"/>
+      <c r="E106" s="27"/>
+      <c r="F106" s="27" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" s="11" t="s">
@@ -4544,7 +4925,8 @@
       <c r="D107" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E107" s="29"/>
+      <c r="E107" s="27"/>
+      <c r="F107" s="27"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" s="11" t="s">
@@ -4559,7 +4941,10 @@
       <c r="D108" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E108" s="29"/>
+      <c r="E108" s="27"/>
+      <c r="F108" s="27" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="109" spans="1:9" ht="87" x14ac:dyDescent="0.35">
       <c r="A109" s="11" t="s">
@@ -4575,8 +4960,11 @@
         <v>188</v>
       </c>
       <c r="E109" s="17"/>
-    </row>
-    <row r="110" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="F109" s="17" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="87" x14ac:dyDescent="0.35">
       <c r="A110" s="11" t="s">
         <v>89</v>
       </c>
@@ -4590,6 +4978,9 @@
         <v>190</v>
       </c>
       <c r="E110" s="13"/>
+      <c r="F110" s="13" t="s">
+        <v>454</v>
+      </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" s="11" t="s">
@@ -4605,6 +4996,9 @@
         <v>100</v>
       </c>
       <c r="E111" s="13"/>
+      <c r="F111" s="13" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" s="11" t="s">
@@ -4620,6 +5014,9 @@
         <v>100</v>
       </c>
       <c r="E112" s="17"/>
+      <c r="F112" s="17" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="11" t="s">
@@ -4635,6 +5032,9 @@
         <v>100</v>
       </c>
       <c r="E113" s="17"/>
+      <c r="F113" s="17" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="114" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A114" s="11" t="s">
@@ -4649,7 +5049,10 @@
       <c r="D114" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E114" s="29"/>
+      <c r="E114" s="27"/>
+      <c r="F114" s="27" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="115" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A115" s="11" t="s">
@@ -4661,10 +5064,13 @@
       <c r="C115" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="D115" s="20" t="s">
+      <c r="D115" s="19" t="s">
         <v>196</v>
       </c>
       <c r="E115" s="17"/>
+      <c r="F115" s="17" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="116" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A116" s="11" t="s">
@@ -4680,6 +5086,7 @@
         <v>100</v>
       </c>
       <c r="E116" s="13"/>
+      <c r="F116" s="13"/>
     </row>
     <row r="117" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A117" s="11" t="s">
@@ -4691,10 +5098,13 @@
       <c r="C117" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="D117" s="30" t="s">
+      <c r="D117" s="28" t="s">
         <v>199</v>
       </c>
-      <c r="E117" s="29"/>
+      <c r="E117" s="27"/>
+      <c r="F117" s="27" t="s">
+        <v>455</v>
+      </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="11" t="s">
@@ -4709,7 +5119,10 @@
       <c r="D118" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E118" s="29"/>
+      <c r="E118" s="27"/>
+      <c r="F118" s="27" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="11" t="s">
@@ -4724,7 +5137,10 @@
       <c r="D119" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E119" s="29"/>
+      <c r="E119" s="27"/>
+      <c r="F119" s="27" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="11" t="s">
@@ -4739,7 +5155,10 @@
       <c r="D120" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E120" s="19"/>
+      <c r="E120" s="18"/>
+      <c r="F120" s="18" t="s">
+        <v>457</v>
+      </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="11" t="s">
@@ -4754,7 +5173,10 @@
       <c r="D121" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E121" s="19"/>
+      <c r="E121" s="18"/>
+      <c r="F121" s="18" t="s">
+        <v>457</v>
+      </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="11" t="s">
@@ -4769,7 +5191,10 @@
       <c r="D122" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E122" s="29"/>
+      <c r="E122" s="27"/>
+      <c r="F122" s="27" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="11" t="s">
@@ -4784,7 +5209,10 @@
       <c r="D123" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E123" s="29"/>
+      <c r="E123" s="27"/>
+      <c r="F123" s="27" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="11" t="s">
@@ -4799,7 +5227,10 @@
       <c r="D124" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E124" s="29"/>
+      <c r="E124" s="27"/>
+      <c r="F124" s="27" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="125" spans="1:6" ht="87" x14ac:dyDescent="0.35">
       <c r="A125" s="11" t="s">
@@ -4814,7 +5245,10 @@
       <c r="D125" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="E125" s="19"/>
+      <c r="E125" s="18"/>
+      <c r="F125" s="18" t="s">
+        <v>457</v>
+      </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" s="11" t="s">
@@ -4829,7 +5263,10 @@
       <c r="D126" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E126" s="29"/>
+      <c r="E126" s="27"/>
+      <c r="F126" s="27" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" s="11" t="s">
@@ -4844,8 +5281,10 @@
       <c r="D127" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E127" s="19"/>
-      <c r="F127" s="31"/>
+      <c r="E127" s="18"/>
+      <c r="F127" s="18" t="s">
+        <v>457</v>
+      </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" s="11" t="s">
@@ -4860,9 +5299,12 @@
       <c r="D128" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E128" s="29"/>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E128" s="27"/>
+      <c r="F128" s="27" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" s="11" t="s">
         <v>89</v>
       </c>
@@ -4875,9 +5317,12 @@
       <c r="D129" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E129" s="29"/>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E129" s="27"/>
+      <c r="F129" s="27" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" s="11" t="s">
         <v>89</v>
       </c>
@@ -4890,9 +5335,12 @@
       <c r="D130" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E130" s="19"/>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E130" s="18"/>
+      <c r="F130" s="18" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" s="11" t="s">
         <v>89</v>
       </c>
@@ -4905,9 +5353,12 @@
       <c r="D131" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E131" s="19"/>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E131" s="18"/>
+      <c r="F131" s="18" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" s="11" t="s">
         <v>89</v>
       </c>
@@ -4920,9 +5371,12 @@
       <c r="D132" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E132" s="32"/>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E132" s="29"/>
+      <c r="F132" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" s="11" t="s">
         <v>89</v>
       </c>
@@ -4935,9 +5389,12 @@
       <c r="D133" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E133" s="19"/>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E133" s="18"/>
+      <c r="F133" s="18" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" s="11" t="s">
         <v>89</v>
       </c>
@@ -4950,9 +5407,12 @@
       <c r="D134" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E134" s="19"/>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E134" s="18"/>
+      <c r="F134" s="18" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" s="11" t="s">
         <v>89</v>
       </c>
@@ -4966,8 +5426,11 @@
         <v>100</v>
       </c>
       <c r="E135" s="13"/>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F135" s="13" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" s="11" t="s">
         <v>89</v>
       </c>
@@ -4980,9 +5443,12 @@
       <c r="D136" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E136" s="29"/>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E136" s="27"/>
+      <c r="F136" s="27" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" s="11" t="s">
         <v>89</v>
       </c>
@@ -4995,9 +5461,12 @@
       <c r="D137" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E137" s="33"/>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E137" s="30"/>
+      <c r="F137" s="30" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" s="11" t="s">
         <v>89</v>
       </c>
@@ -5010,9 +5479,12 @@
       <c r="D138" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E138" s="29"/>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E138" s="27"/>
+      <c r="F138" s="27" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" s="11" t="s">
         <v>89</v>
       </c>
@@ -5025,9 +5497,12 @@
       <c r="D139" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E139" s="29"/>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E139" s="27"/>
+      <c r="F139" s="27" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" s="11" t="s">
         <v>89</v>
       </c>
@@ -5040,9 +5515,12 @@
       <c r="D140" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E140" s="29"/>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E140" s="27"/>
+      <c r="F140" s="27" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" s="11" t="s">
         <v>89</v>
       </c>
@@ -5055,9 +5533,12 @@
       <c r="D141" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E141" s="29"/>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E141" s="27"/>
+      <c r="F141" s="27" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" s="11" t="s">
         <v>89</v>
       </c>
@@ -5070,9 +5551,12 @@
       <c r="D142" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E142" s="34"/>
-    </row>
-    <row r="143" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="E142" s="31"/>
+      <c r="F142" s="31" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A143" s="11" t="s">
         <v>89</v>
       </c>
@@ -5085,9 +5569,12 @@
       <c r="D143" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="E143" s="29"/>
-    </row>
-    <row r="144" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="E143" s="27"/>
+      <c r="F143" s="27" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A144" s="11" t="s">
         <v>89</v>
       </c>
@@ -5100,7 +5587,10 @@
       <c r="D144" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="E144" s="19"/>
+      <c r="E144" s="18"/>
+      <c r="F144" s="18" t="s">
+        <v>457</v>
+      </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" s="11" t="s">
@@ -5115,7 +5605,10 @@
       <c r="D145" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E145" s="19"/>
+      <c r="E145" s="18"/>
+      <c r="F145" s="18" t="s">
+        <v>457</v>
+      </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" s="11" t="s">
@@ -5130,7 +5623,10 @@
       <c r="D146" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E146" s="19"/>
+      <c r="E146" s="18"/>
+      <c r="F146" s="18" t="s">
+        <v>457</v>
+      </c>
     </row>
     <row r="147" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A147" s="11" t="s">
@@ -5145,7 +5641,10 @@
       <c r="D147" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E147" s="29"/>
+      <c r="E147" s="27"/>
+      <c r="F147" s="27" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" s="11" t="s">
@@ -5160,7 +5659,10 @@
       <c r="D148" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E148" s="29"/>
+      <c r="E148" s="27"/>
+      <c r="F148" s="27" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="149" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A149" s="11" t="s">
@@ -5176,6 +5678,9 @@
         <v>232</v>
       </c>
       <c r="E149" s="12"/>
+      <c r="F149" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" s="11" t="s">
@@ -5191,6 +5696,9 @@
         <v>100</v>
       </c>
       <c r="E150" s="12"/>
+      <c r="F150" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" s="11" t="s">
@@ -5206,6 +5714,9 @@
         <v>235</v>
       </c>
       <c r="E151" s="12"/>
+      <c r="F151" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="152" spans="1:6" ht="174" x14ac:dyDescent="0.35">
       <c r="A152" s="11" t="s">
@@ -5221,7 +5732,9 @@
         <v>237</v>
       </c>
       <c r="E152" s="17"/>
-      <c r="F152" s="18"/>
+      <c r="F152" s="17" t="s">
+        <v>460</v>
+      </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153" s="11" t="s">
@@ -5233,8 +5746,11 @@
       <c r="C153" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="D153" s="20"/>
-      <c r="E153" s="29"/>
+      <c r="D153" s="19"/>
+      <c r="E153" s="27"/>
+      <c r="F153" s="27" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154" s="11" t="s">
@@ -5247,7 +5763,10 @@
         <v>239</v>
       </c>
       <c r="D154" s="9"/>
-      <c r="E154" s="29"/>
+      <c r="E154" s="27"/>
+      <c r="F154" s="27" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155" s="11" t="s">
@@ -5262,9 +5781,12 @@
       <c r="D155" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E155" s="29"/>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E155" s="27"/>
+      <c r="F155" s="27" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A156" s="11" t="s">
         <v>89</v>
       </c>
@@ -5277,8 +5799,10 @@
       <c r="D156" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E156" s="19"/>
-      <c r="F156" s="31"/>
+      <c r="E156" s="18"/>
+      <c r="F156" s="18" t="s">
+        <v>461</v>
+      </c>
     </row>
     <row r="157" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A157" s="11" t="s">
@@ -5287,14 +5811,16 @@
       <c r="B157" s="5">
         <v>112</v>
       </c>
-      <c r="C157" s="35" t="s">
+      <c r="C157" s="32" t="s">
         <v>242</v>
       </c>
-      <c r="D157" s="20" t="s">
+      <c r="D157" s="19" t="s">
         <v>243</v>
       </c>
       <c r="E157" s="12"/>
-      <c r="F157" s="31"/>
+      <c r="F157" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="158" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A158" s="11" t="s">
@@ -5309,8 +5835,10 @@
       <c r="D158" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="E158" s="19"/>
-      <c r="F158" s="31"/>
+      <c r="E158" s="18"/>
+      <c r="F158" s="18" t="s">
+        <v>462</v>
+      </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A159" s="11" t="s">
@@ -5325,7 +5853,10 @@
       <c r="D159" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E159" s="29"/>
+      <c r="E159" s="27"/>
+      <c r="F159" s="27" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="160" spans="1:6" ht="87" x14ac:dyDescent="0.35">
       <c r="A160" s="11" t="s">
@@ -5341,6 +5872,9 @@
         <v>248</v>
       </c>
       <c r="E160" s="13"/>
+      <c r="F160" s="13" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161" s="11" t="s">
@@ -5356,6 +5890,9 @@
         <v>100</v>
       </c>
       <c r="E161" s="13"/>
+      <c r="F161" s="13" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="162" spans="1:6" ht="32" x14ac:dyDescent="0.35">
       <c r="A162" s="11" t="s">
@@ -5367,10 +5904,13 @@
       <c r="C162" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="D162" s="36" t="s">
+      <c r="D162" s="33" t="s">
         <v>251</v>
       </c>
-      <c r="E162" s="32"/>
+      <c r="E162" s="29"/>
+      <c r="F162" s="29" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163" s="11" t="s">
@@ -5386,6 +5926,7 @@
         <v>100</v>
       </c>
       <c r="E163" s="13"/>
+      <c r="F163" s="13"/>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A164" s="11" t="s">
@@ -5400,7 +5941,10 @@
       <c r="D164" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E164" s="32"/>
+      <c r="E164" s="29"/>
+      <c r="F164" s="29" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="165" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A165" s="11" t="s">
@@ -5415,7 +5959,10 @@
       <c r="D165" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="E165" s="37"/>
+      <c r="E165" s="34"/>
+      <c r="F165" s="34" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="166" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A166" s="11" t="s">
@@ -5430,7 +5977,10 @@
       <c r="D166" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="E166" s="32"/>
+      <c r="E166" s="29"/>
+      <c r="F166" s="29" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="167" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A167" s="11" t="s">
@@ -5445,9 +5995,12 @@
       <c r="D167" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="E167" s="19"/>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E167" s="18"/>
+      <c r="F167" s="18" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A168" s="11" t="s">
         <v>89</v>
       </c>
@@ -5460,7 +6013,10 @@
       <c r="D168" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E168" s="19"/>
+      <c r="E168" s="18"/>
+      <c r="F168" s="18" t="s">
+        <v>465</v>
+      </c>
     </row>
     <row r="169" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A169" s="11" t="s">
@@ -5469,13 +6025,16 @@
       <c r="B169" s="5">
         <v>124</v>
       </c>
-      <c r="C169" s="38" t="s">
+      <c r="C169" s="35" t="s">
         <v>261</v>
       </c>
-      <c r="D169" s="20" t="s">
+      <c r="D169" s="19" t="s">
         <v>262</v>
       </c>
       <c r="E169" s="13"/>
+      <c r="F169" s="13" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="170" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A170" s="11" t="s">
@@ -5490,7 +6049,10 @@
       <c r="D170" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="E170" s="19"/>
+      <c r="E170" s="18"/>
+      <c r="F170" s="18" t="s">
+        <v>466</v>
+      </c>
     </row>
     <row r="171" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A171" s="11" t="s">
@@ -5499,13 +6061,16 @@
       <c r="B171" s="5">
         <v>126</v>
       </c>
-      <c r="C171" s="39" t="s">
+      <c r="C171" s="36" t="s">
         <v>265</v>
       </c>
-      <c r="D171" s="20" t="s">
+      <c r="D171" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="E171" s="32"/>
+      <c r="E171" s="29"/>
+      <c r="F171" s="29" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172" s="11" t="s">
@@ -5520,7 +6085,10 @@
       <c r="D172" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E172" s="19"/>
+      <c r="E172" s="18"/>
+      <c r="F172" s="18" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" s="11" t="s">
@@ -5535,8 +6103,10 @@
       <c r="D173" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E173" s="19"/>
-      <c r="F173" s="31"/>
+      <c r="E173" s="18"/>
+      <c r="F173" s="18" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A174" s="11" t="s">
@@ -5551,7 +6121,10 @@
       <c r="D174" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E174" s="19"/>
+      <c r="E174" s="18"/>
+      <c r="F174" s="18" t="s">
+        <v>457</v>
+      </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A175" s="11" t="s">
@@ -5566,7 +6139,10 @@
       <c r="D175" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E175" s="19"/>
+      <c r="E175" s="18"/>
+      <c r="F175" s="18" t="s">
+        <v>457</v>
+      </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A176" s="11" t="s">
@@ -5581,9 +6157,12 @@
       <c r="D176" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E176" s="19"/>
-    </row>
-    <row r="177" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="E176" s="18"/>
+      <c r="F176" s="18" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="87" x14ac:dyDescent="0.35">
       <c r="A177" s="11" t="s">
         <v>89</v>
       </c>
@@ -5596,10 +6175,13 @@
       <c r="D177" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="E177" s="29"/>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A178" s="40" t="s">
+      <c r="E177" s="27"/>
+      <c r="F177" s="27" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A178" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B178" s="5">
@@ -5611,10 +6193,13 @@
       <c r="D178" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E178" s="32"/>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A179" s="40" t="s">
+      <c r="E178" s="29"/>
+      <c r="F178" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A179" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B179" s="5">
@@ -5626,10 +6211,13 @@
       <c r="D179" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E179" s="19"/>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A180" s="40" t="s">
+      <c r="E179" s="18"/>
+      <c r="F179" s="18" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A180" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B180" s="5">
@@ -5639,10 +6227,13 @@
         <v>180</v>
       </c>
       <c r="D180" s="9"/>
-      <c r="E180" s="19"/>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A181" s="40" t="s">
+      <c r="E180" s="18"/>
+      <c r="F180" s="18" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A181" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B181" s="5">
@@ -5654,10 +6245,13 @@
       <c r="D181" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E181" s="19"/>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A182" s="40" t="s">
+      <c r="E181" s="18"/>
+      <c r="F181" s="18" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A182" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B182" s="5">
@@ -5666,13 +6260,16 @@
       <c r="C182" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D182" s="41" t="s">
+      <c r="D182" s="38" t="s">
         <v>278</v>
       </c>
-      <c r="E182" s="19"/>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A183" s="40" t="s">
+      <c r="E182" s="18"/>
+      <c r="F182" s="18" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A183" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B183" s="5">
@@ -5684,40 +6281,49 @@
       <c r="D183" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E183" s="19"/>
-    </row>
-    <row r="184" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A184" s="40" t="s">
+      <c r="E183" s="18"/>
+      <c r="F183" s="18" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A184" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B184" s="5">
         <v>7</v>
       </c>
-      <c r="C184" s="38" t="s">
+      <c r="C184" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="D184" s="20" t="s">
+      <c r="D184" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="E184" s="32"/>
-    </row>
-    <row r="185" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A185" s="40" t="s">
+      <c r="E184" s="29"/>
+      <c r="F184" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A185" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B185" s="5">
         <v>8</v>
       </c>
-      <c r="C185" s="42" t="s">
+      <c r="C185" s="39" t="s">
         <v>280</v>
       </c>
-      <c r="D185" s="20" t="s">
+      <c r="D185" s="19" t="s">
         <v>281</v>
       </c>
-      <c r="E185" s="32"/>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A186" s="40" t="s">
+      <c r="E185" s="29"/>
+      <c r="F185" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A186" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B186" s="5">
@@ -5729,10 +6335,13 @@
       <c r="D186" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E186" s="19"/>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A187" s="40" t="s">
+      <c r="E186" s="18"/>
+      <c r="F186" s="18" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A187" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B187" s="5">
@@ -5745,9 +6354,10 @@
         <v>100</v>
       </c>
       <c r="E187" s="13"/>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A188" s="40" t="s">
+      <c r="F187" s="13"/>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A188" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B188" s="5">
@@ -5758,9 +6368,10 @@
       </c>
       <c r="D188" s="9"/>
       <c r="E188" s="13"/>
-    </row>
-    <row r="189" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A189" s="40" t="s">
+      <c r="F188" s="13"/>
+    </row>
+    <row r="189" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A189" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B189" s="5">
@@ -5772,10 +6383,13 @@
       <c r="D189" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="E189" s="32"/>
-    </row>
-    <row r="190" spans="1:5" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A190" s="40" t="s">
+      <c r="E189" s="29"/>
+      <c r="F189" s="29" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A190" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B190" s="5">
@@ -5787,10 +6401,13 @@
       <c r="D190" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="E190" s="43"/>
-    </row>
-    <row r="191" spans="1:5" ht="290" x14ac:dyDescent="0.35">
-      <c r="A191" s="40" t="s">
+      <c r="E190" s="40"/>
+      <c r="F190" s="40" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" ht="290" x14ac:dyDescent="0.35">
+      <c r="A191" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B191" s="5">
@@ -5802,10 +6419,13 @@
       <c r="D191" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="E191" s="43"/>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A192" s="40" t="s">
+      <c r="E191" s="40"/>
+      <c r="F191" s="40" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A192" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B192" s="5">
@@ -5818,9 +6438,10 @@
         <v>100</v>
       </c>
       <c r="E192" s="13"/>
+      <c r="F192" s="13"/>
     </row>
     <row r="193" spans="1:6" ht="39" x14ac:dyDescent="0.35">
-      <c r="A193" s="40" t="s">
+      <c r="A193" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B193" s="5">
@@ -5829,13 +6450,16 @@
       <c r="C193" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="D193" s="26" t="s">
+      <c r="D193" s="24" t="s">
         <v>293</v>
       </c>
-      <c r="E193" s="19"/>
+      <c r="E193" s="18"/>
+      <c r="F193" s="18" t="s">
+        <v>470</v>
+      </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A194" s="40" t="s">
+      <c r="A194" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B194" s="5">
@@ -5848,9 +6472,10 @@
         <v>100</v>
       </c>
       <c r="E194" s="13"/>
+      <c r="F194" s="13"/>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A195" s="40" t="s">
+      <c r="A195" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B195" s="5">
@@ -5862,10 +6487,13 @@
       <c r="D195" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E195" s="32"/>
+      <c r="E195" s="29"/>
+      <c r="F195" s="29" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A196" s="40" t="s">
+      <c r="A196" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B196" s="5">
@@ -5877,10 +6505,13 @@
       <c r="D196" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E196" s="32"/>
+      <c r="E196" s="29"/>
+      <c r="F196" s="29" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A197" s="40" t="s">
+      <c r="A197" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B197" s="5">
@@ -5892,10 +6523,13 @@
       <c r="D197" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E197" s="32"/>
+      <c r="E197" s="29"/>
+      <c r="F197" s="29" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="198" spans="1:6" ht="145" x14ac:dyDescent="0.35">
-      <c r="A198" s="40" t="s">
+      <c r="A198" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B198" s="5">
@@ -5907,11 +6541,13 @@
       <c r="D198" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="E198" s="19"/>
-      <c r="F198" s="18"/>
+      <c r="E198" s="18"/>
+      <c r="F198" s="18" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A199" s="40" t="s">
+      <c r="A199" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B199" s="5">
@@ -5923,10 +6559,13 @@
       <c r="D199" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E199" s="19"/>
+      <c r="E199" s="18"/>
+      <c r="F199" s="18" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A200" s="40" t="s">
+      <c r="A200" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B200" s="5">
@@ -5938,10 +6577,13 @@
       <c r="D200" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E200" s="19"/>
+      <c r="E200" s="18"/>
+      <c r="F200" s="18" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A201" s="40" t="s">
+      <c r="A201" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B201" s="5">
@@ -5953,10 +6595,13 @@
       <c r="D201" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E201" s="32"/>
+      <c r="E201" s="29"/>
+      <c r="F201" s="29" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="202" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A202" s="40" t="s">
+      <c r="A202" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B202" s="5">
@@ -5968,10 +6613,13 @@
       <c r="D202" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E202" s="32"/>
+      <c r="E202" s="29"/>
+      <c r="F202" s="29" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="203" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A203" s="40" t="s">
+      <c r="A203" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B203" s="5">
@@ -5983,10 +6631,13 @@
       <c r="D203" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E203" s="32"/>
+      <c r="E203" s="29"/>
+      <c r="F203" s="29" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A204" s="40" t="s">
+      <c r="A204" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B204" s="5">
@@ -5998,10 +6649,13 @@
       <c r="D204" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E204" s="19"/>
+      <c r="E204" s="18"/>
+      <c r="F204" s="18" t="s">
+        <v>471</v>
+      </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A205" s="40" t="s">
+      <c r="A205" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B205" s="5">
@@ -6013,10 +6667,13 @@
       <c r="D205" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E205" s="19"/>
+      <c r="E205" s="18"/>
+      <c r="F205" s="18" t="s">
+        <v>471</v>
+      </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A206" s="40" t="s">
+      <c r="A206" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B206" s="5">
@@ -6026,10 +6683,13 @@
         <v>307</v>
       </c>
       <c r="D206" s="9"/>
-      <c r="E206" s="32"/>
+      <c r="E206" s="29"/>
+      <c r="F206" s="29" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="207" spans="1:6" ht="176.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A207" s="40" t="s">
+      <c r="A207" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B207" s="5">
@@ -6041,10 +6701,13 @@
       <c r="D207" s="9" t="s">
         <v>309</v>
       </c>
-      <c r="E207" s="44"/>
+      <c r="E207" s="41"/>
+      <c r="F207" s="41" t="s">
+        <v>472</v>
+      </c>
     </row>
     <row r="208" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A208" s="40" t="s">
+      <c r="A208" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B208" s="5">
@@ -6056,10 +6719,13 @@
       <c r="D208" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="E208" s="44"/>
-    </row>
-    <row r="209" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A209" s="40" t="s">
+      <c r="E208" s="41"/>
+      <c r="F208" s="41" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A209" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B209" s="5">
@@ -6071,10 +6737,13 @@
       <c r="D209" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="E209" s="44"/>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A210" s="40" t="s">
+      <c r="E209" s="41"/>
+      <c r="F209" s="41" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A210" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B210" s="5">
@@ -6087,9 +6756,12 @@
         <v>100</v>
       </c>
       <c r="E210"/>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A211" s="40" t="s">
+      <c r="F210" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A211" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B211" s="5">
@@ -6101,10 +6773,13 @@
       <c r="D211" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E211" s="32"/>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A212" s="40" t="s">
+      <c r="E211" s="29"/>
+      <c r="F211" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A212" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B212" s="5">
@@ -6116,10 +6791,13 @@
       <c r="D212" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E212" s="32"/>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A213" s="40" t="s">
+      <c r="E212" s="29"/>
+      <c r="F212" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A213" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B213" s="5">
@@ -6131,10 +6809,13 @@
       <c r="D213" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E213" s="32"/>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A214" s="40" t="s">
+      <c r="E213" s="29"/>
+      <c r="F213" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A214" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B214" s="5">
@@ -6146,10 +6827,13 @@
       <c r="D214" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E214" s="44"/>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A215" s="40" t="s">
+      <c r="E214" s="41"/>
+      <c r="F214" s="41" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A215" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B215" s="5">
@@ -6161,10 +6845,13 @@
       <c r="D215" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E215" s="44"/>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A216" s="40" t="s">
+      <c r="E215" s="41"/>
+      <c r="F215" s="41" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A216" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B216" s="5">
@@ -6176,10 +6863,13 @@
       <c r="D216" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E216" s="44"/>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A217" s="40" t="s">
+      <c r="E216" s="41"/>
+      <c r="F216" s="41" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A217" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B217" s="5">
@@ -6191,10 +6881,13 @@
       <c r="D217" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E217" s="19"/>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A218" s="40" t="s">
+      <c r="E217" s="18"/>
+      <c r="F217" s="18" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A218" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B218" s="5">
@@ -6206,10 +6899,13 @@
       <c r="D218" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E218" s="32"/>
-    </row>
-    <row r="219" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A219" s="40" t="s">
+      <c r="E218" s="29"/>
+      <c r="F218" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A219" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B219" s="5">
@@ -6221,10 +6917,13 @@
       <c r="D219" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="E219" s="32"/>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A220" s="40" t="s">
+      <c r="E219" s="29"/>
+      <c r="F219" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A220" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B220" s="5">
@@ -6236,10 +6935,13 @@
       <c r="D220" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E220" s="32"/>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A221" s="40" t="s">
+      <c r="E220" s="29"/>
+      <c r="F220" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A221" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B221" s="5">
@@ -6251,10 +6953,13 @@
       <c r="D221" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E221" s="32"/>
-    </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A222" s="40" t="s">
+      <c r="E221" s="29"/>
+      <c r="F221" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A222" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B222" s="5">
@@ -6266,10 +6971,13 @@
       <c r="D222" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="E222" s="32"/>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A223" s="40" t="s">
+      <c r="E222" s="29"/>
+      <c r="F222" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A223" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B223" s="5">
@@ -6281,10 +6989,13 @@
       <c r="D223" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E223" s="19"/>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A224" s="40" t="s">
+      <c r="E223" s="18"/>
+      <c r="F223" s="18" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A224" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B224" s="5">
@@ -6296,10 +7007,13 @@
       <c r="D224" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E224" s="32"/>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A225" s="40" t="s">
+      <c r="E224" s="29"/>
+      <c r="F224" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A225" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B225" s="5">
@@ -6311,10 +7025,13 @@
       <c r="D225" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E225" s="32"/>
-    </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A226" s="40" t="s">
+      <c r="E225" s="29"/>
+      <c r="F225" s="29" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A226" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B226" s="5">
@@ -6326,10 +7043,13 @@
       <c r="D226" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E226" s="19"/>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A227" s="40" t="s">
+      <c r="E226" s="18"/>
+      <c r="F226" s="18" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A227" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B227" s="5">
@@ -6341,10 +7061,13 @@
       <c r="D227" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E227" s="32"/>
-    </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A228" s="40" t="s">
+      <c r="E227" s="29"/>
+      <c r="F227" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A228" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B228" s="5">
@@ -6356,10 +7079,13 @@
       <c r="D228" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E228" s="19"/>
-    </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A229" s="40" t="s">
+      <c r="E228" s="18"/>
+      <c r="F228" s="18" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A229" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B229" s="5">
@@ -6371,10 +7097,13 @@
       <c r="D229" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E229" s="32"/>
-    </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A230" s="40" t="s">
+      <c r="E229" s="29"/>
+      <c r="F229" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A230" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B230" s="5">
@@ -6386,10 +7115,13 @@
       <c r="D230" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E230" s="32"/>
-    </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A231" s="40" t="s">
+      <c r="E230" s="29"/>
+      <c r="F230" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A231" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B231" s="5">
@@ -6401,10 +7133,13 @@
       <c r="D231" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E231" s="32"/>
-    </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A232" s="40" t="s">
+      <c r="E231" s="29"/>
+      <c r="F231" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A232" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B232" s="5">
@@ -6416,10 +7151,13 @@
       <c r="D232" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E232" s="19"/>
-    </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A233" s="40" t="s">
+      <c r="E232" s="18"/>
+      <c r="F232" s="18" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A233" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B233" s="5">
@@ -6431,10 +7169,13 @@
       <c r="D233" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E233" s="32"/>
-    </row>
-    <row r="234" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A234" s="40" t="s">
+      <c r="E233" s="29"/>
+      <c r="F233" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A234" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B234" s="5">
@@ -6447,9 +7188,12 @@
         <v>336</v>
       </c>
       <c r="E234" s="17"/>
-    </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A235" s="40" t="s">
+      <c r="F234" s="17" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A235" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B235" s="5">
@@ -6462,9 +7206,12 @@
         <v>100</v>
       </c>
       <c r="E235" s="17"/>
-    </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A236" s="40" t="s">
+      <c r="F235" s="17" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A236" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B236" s="5">
@@ -6477,9 +7224,12 @@
         <v>100</v>
       </c>
       <c r="E236" s="17"/>
-    </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A237" s="40" t="s">
+      <c r="F236" s="17" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A237" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B237" s="5">
@@ -6491,10 +7241,13 @@
       <c r="D237" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E237" s="29"/>
-    </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A238" s="40" t="s">
+      <c r="E237" s="27"/>
+      <c r="F237" s="27" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A238" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B238" s="5">
@@ -6507,9 +7260,12 @@
         <v>100</v>
       </c>
       <c r="E238" s="13"/>
-    </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A239" s="40" t="s">
+      <c r="F238" s="13" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A239" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B239" s="5">
@@ -6521,10 +7277,13 @@
       <c r="D239" s="9" t="s">
         <v>342</v>
       </c>
-      <c r="E239" s="29"/>
-    </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A240" s="40" t="s">
+      <c r="E239" s="27"/>
+      <c r="F239" s="27" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A240" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B240" s="5">
@@ -6536,10 +7295,13 @@
       <c r="D240" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E240" s="29"/>
-    </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A241" s="40" t="s">
+      <c r="E240" s="27"/>
+      <c r="F240" s="27" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A241" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B241" s="5">
@@ -6551,10 +7313,13 @@
       <c r="D241" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="E241" s="29"/>
-    </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A242" s="40" t="s">
+      <c r="E241" s="27"/>
+      <c r="F241" s="27" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A242" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B242" s="5">
@@ -6566,10 +7331,13 @@
       <c r="D242" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E242" s="29"/>
-    </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A243" s="40" t="s">
+      <c r="E242" s="27"/>
+      <c r="F242" s="27" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A243" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B243" s="5">
@@ -6582,9 +7350,12 @@
         <v>100</v>
       </c>
       <c r="E243" s="17"/>
-    </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A244" s="40" t="s">
+      <c r="F243" s="17" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A244" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B244" s="5">
@@ -6597,9 +7368,12 @@
         <v>349</v>
       </c>
       <c r="E244" s="13"/>
-    </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A245" s="40" t="s">
+      <c r="F244" s="13" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A245" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B245" s="5">
@@ -6611,10 +7385,13 @@
       <c r="D245" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E245" s="29"/>
-    </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A246" s="40" t="s">
+      <c r="E245" s="27"/>
+      <c r="F245" s="27" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A246" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B246" s="5">
@@ -6626,10 +7403,13 @@
       <c r="D246" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E246" s="29"/>
-    </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A247" s="40" t="s">
+      <c r="E246" s="27"/>
+      <c r="F246" s="27" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A247" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B247" s="5">
@@ -6639,10 +7419,13 @@
         <v>352</v>
       </c>
       <c r="D247" s="9"/>
-      <c r="E247" s="29"/>
-    </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A248" s="40" t="s">
+      <c r="E247" s="27"/>
+      <c r="F247" s="27" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A248" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B248" s="5">
@@ -6654,10 +7437,13 @@
       <c r="D248" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E248" s="29"/>
-    </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A249" s="40" t="s">
+      <c r="E248" s="27"/>
+      <c r="F248" s="27" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A249" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B249" s="5">
@@ -6670,9 +7456,12 @@
         <v>100</v>
       </c>
       <c r="E249" s="17"/>
-    </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A250" s="40" t="s">
+      <c r="F249" s="17" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A250" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B250" s="5">
@@ -6684,10 +7473,13 @@
       <c r="D250" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E250" s="19"/>
-    </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A251" s="40" t="s">
+      <c r="E250" s="18"/>
+      <c r="F250" s="18" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A251" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B251" s="5">
@@ -6699,10 +7491,13 @@
       <c r="D251" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E251" s="29"/>
-    </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A252" s="40" t="s">
+      <c r="E251" s="27"/>
+      <c r="F251" s="27" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A252" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B252" s="5">
@@ -6714,10 +7509,13 @@
       <c r="D252" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E252" s="29"/>
-    </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A253" s="40" t="s">
+      <c r="E252" s="27"/>
+      <c r="F252" s="27" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A253" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B253" s="5">
@@ -6729,10 +7527,13 @@
       <c r="D253" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E253" s="29"/>
-    </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A254" s="40" t="s">
+      <c r="E253" s="27"/>
+      <c r="F253" s="27" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A254" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B254" s="5">
@@ -6744,10 +7545,13 @@
       <c r="D254" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E254" s="29"/>
-    </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A255" s="40" t="s">
+      <c r="E254" s="27"/>
+      <c r="F254" s="27" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A255" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B255" s="5">
@@ -6760,9 +7564,12 @@
         <v>100</v>
       </c>
       <c r="E255" s="17"/>
-    </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A256" s="40" t="s">
+      <c r="F255" s="17" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A256" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B256" s="5">
@@ -6774,10 +7581,13 @@
       <c r="D256" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E256" s="29"/>
-    </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A257" s="40" t="s">
+      <c r="E256" s="27"/>
+      <c r="F256" s="27" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A257" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B257" s="5">
@@ -6789,10 +7599,13 @@
       <c r="D257" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E257" s="29"/>
-    </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A258" s="40" t="s">
+      <c r="E257" s="27"/>
+      <c r="F257" s="27" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A258" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B258" s="5">
@@ -6804,10 +7617,13 @@
       <c r="D258" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E258" s="29"/>
-    </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A259" s="40" t="s">
+      <c r="E258" s="27"/>
+      <c r="F258" s="27" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A259" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B259" s="5">
@@ -6819,10 +7635,13 @@
       <c r="D259" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E259" s="29"/>
-    </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A260" s="40" t="s">
+      <c r="E259" s="27"/>
+      <c r="F259" s="27" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A260" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B260" s="5">
@@ -6834,10 +7653,13 @@
       <c r="D260" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E260" s="29"/>
-    </row>
-    <row r="261" spans="1:5" ht="174" x14ac:dyDescent="0.35">
-      <c r="A261" s="40" t="s">
+      <c r="E260" s="27"/>
+      <c r="F260" s="27" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" ht="174" x14ac:dyDescent="0.35">
+      <c r="A261" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B261" s="5">
@@ -6849,10 +7671,13 @@
       <c r="D261" s="9" t="s">
         <v>366</v>
       </c>
-      <c r="E261" s="29"/>
-    </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A262" s="40" t="s">
+      <c r="E261" s="27"/>
+      <c r="F261" s="27" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A262" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B262" s="5">
@@ -6864,10 +7689,13 @@
       <c r="D262" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E262" s="32"/>
-    </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A263" s="40" t="s">
+      <c r="E262" s="29"/>
+      <c r="F262" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A263" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B263" s="5">
@@ -6879,10 +7707,13 @@
       <c r="D263" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E263" s="32"/>
-    </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A264" s="40" t="s">
+      <c r="E263" s="29"/>
+      <c r="F263" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A264" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B264" s="5">
@@ -6894,10 +7725,13 @@
       <c r="D264" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E264" s="19"/>
-    </row>
-    <row r="265" spans="1:5" ht="26" x14ac:dyDescent="0.35">
-      <c r="A265" s="40" t="s">
+      <c r="E264" s="18"/>
+      <c r="F264" s="18" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A265" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B265" s="5">
@@ -6906,13 +7740,16 @@
       <c r="C265" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="D265" s="26" t="s">
+      <c r="D265" s="24" t="s">
         <v>369</v>
       </c>
       <c r="E265" s="17"/>
-    </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A266" s="40" t="s">
+      <c r="F265" s="17" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A266" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B266" s="5">
@@ -6924,10 +7761,13 @@
       <c r="D266" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E266" s="32"/>
-    </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A267" s="40" t="s">
+      <c r="E266" s="29"/>
+      <c r="F266" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A267" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B267" s="5">
@@ -6939,10 +7779,13 @@
       <c r="D267" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E267" s="32"/>
-    </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A268" s="40" t="s">
+      <c r="E267" s="29"/>
+      <c r="F267" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A268" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B268" s="5">
@@ -6954,10 +7797,13 @@
       <c r="D268" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E268" s="32"/>
-    </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A269" s="40" t="s">
+      <c r="E268" s="29"/>
+      <c r="F268" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A269" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B269" s="5">
@@ -6970,9 +7816,12 @@
         <v>100</v>
       </c>
       <c r="E269" s="17"/>
-    </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A270" s="40" t="s">
+      <c r="F269" s="17" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A270" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B270" s="5">
@@ -6984,10 +7833,13 @@
       <c r="D270" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="E270" s="29"/>
-    </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A271" s="40" t="s">
+      <c r="E270" s="27"/>
+      <c r="F270" s="27" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A271" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B271" s="5">
@@ -7000,9 +7852,12 @@
         <v>100</v>
       </c>
       <c r="E271" s="17"/>
-    </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A272" s="40" t="s">
+      <c r="F271" s="17" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A272" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B272" s="5">
@@ -7015,9 +7870,12 @@
         <v>100</v>
       </c>
       <c r="E272" s="17"/>
-    </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A273" s="40" t="s">
+      <c r="F272" s="17" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A273" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B273" s="5">
@@ -7029,10 +7887,13 @@
       <c r="D273" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E273" s="19"/>
-    </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A274" s="40" t="s">
+      <c r="E273" s="18"/>
+      <c r="F273" s="18" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A274" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B274" s="5">
@@ -7045,9 +7906,12 @@
         <v>100</v>
       </c>
       <c r="E274" s="17"/>
-    </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A275" s="40" t="s">
+      <c r="F274" s="17" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A275" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B275" s="5">
@@ -7059,10 +7923,13 @@
       <c r="D275" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="E275" s="32"/>
-    </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A276" s="40" t="s">
+      <c r="E275" s="29"/>
+      <c r="F275" s="29" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A276" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B276" s="5">
@@ -7075,9 +7942,12 @@
         <v>100</v>
       </c>
       <c r="E276" s="17"/>
-    </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A277" s="40" t="s">
+      <c r="F276" s="17" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A277" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B277" s="5">
@@ -7089,10 +7959,13 @@
       <c r="D277" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E277" s="32"/>
-    </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A278" s="40" t="s">
+      <c r="E277" s="29"/>
+      <c r="F277" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A278" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B278" s="5">
@@ -7105,9 +7978,12 @@
         <v>100</v>
       </c>
       <c r="E278" s="17"/>
-    </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A279" s="40" t="s">
+      <c r="F278" s="17" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A279" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B279" s="5">
@@ -7120,9 +7996,12 @@
         <v>100</v>
       </c>
       <c r="E279" s="17"/>
-    </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A280" s="40" t="s">
+      <c r="F279" s="17" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A280" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B280" s="5">
@@ -7134,10 +8013,13 @@
       <c r="D280" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E280" s="32"/>
-    </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A281" s="40" t="s">
+      <c r="E280" s="29"/>
+      <c r="F280" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A281" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B281" s="5">
@@ -7149,10 +8031,13 @@
       <c r="D281" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E281" s="32"/>
-    </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A282" s="40" t="s">
+      <c r="E281" s="29"/>
+      <c r="F281" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A282" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B282" s="5">
@@ -7164,10 +8049,13 @@
       <c r="D282" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E282" s="32"/>
-    </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A283" s="40" t="s">
+      <c r="E282" s="29"/>
+      <c r="F282" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A283" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B283" s="5">
@@ -7179,10 +8067,13 @@
       <c r="D283" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E283" s="32"/>
-    </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A284" s="40" t="s">
+      <c r="E283" s="29"/>
+      <c r="F283" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A284" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B284" s="5">
@@ -7192,10 +8083,13 @@
         <v>390</v>
       </c>
       <c r="D284" s="9"/>
-      <c r="E284" s="32"/>
-    </row>
-    <row r="285" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A285" s="40" t="s">
+      <c r="E284" s="29"/>
+      <c r="F284" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A285" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B285" s="5">
@@ -7208,9 +8102,12 @@
         <v>392</v>
       </c>
       <c r="E285" s="17"/>
-    </row>
-    <row r="286" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A286" s="40" t="s">
+      <c r="F285" s="17" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A286" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B286" s="5">
@@ -7222,10 +8119,13 @@
       <c r="D286" s="9" t="s">
         <v>394</v>
       </c>
-      <c r="E286" s="32"/>
-    </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A287" s="40" t="s">
+      <c r="E286" s="29"/>
+      <c r="F286" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A287" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B287" s="5">
@@ -7237,10 +8137,13 @@
       <c r="D287" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E287" s="19"/>
-    </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A288" s="40" t="s">
+      <c r="E287" s="18"/>
+      <c r="F287" s="18" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A288" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B288" s="5">
@@ -7252,10 +8155,13 @@
       <c r="D288" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E288" s="32"/>
-    </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A289" s="40" t="s">
+      <c r="E288" s="29"/>
+      <c r="F288" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A289" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B289" s="5">
@@ -7267,10 +8173,13 @@
       <c r="D289" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E289" s="32"/>
-    </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A290" s="40" t="s">
+      <c r="E289" s="29"/>
+      <c r="F289" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A290" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B290" s="5">
@@ -7282,10 +8191,13 @@
       <c r="D290" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E290" s="19"/>
-    </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A291" s="40" t="s">
+      <c r="E290" s="18"/>
+      <c r="F290" s="18" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A291" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B291" s="5">
@@ -7297,10 +8209,13 @@
       <c r="D291" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E291" s="45"/>
-    </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A292" s="40" t="s">
+      <c r="E291" s="42"/>
+      <c r="F291" s="42" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A292" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B292" s="5">
@@ -7312,10 +8227,13 @@
       <c r="D292" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E292" s="45"/>
-    </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A293" s="40" t="s">
+      <c r="E292" s="42"/>
+      <c r="F292" s="42" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A293" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B293" s="5">
@@ -7327,10 +8245,13 @@
       <c r="D293" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E293" s="45"/>
-    </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A294" s="40" t="s">
+      <c r="E293" s="42"/>
+      <c r="F293" s="42" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A294" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B294" s="5">
@@ -7342,10 +8263,13 @@
       <c r="D294" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E294" s="45"/>
-    </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A295" s="40" t="s">
+      <c r="E294" s="42"/>
+      <c r="F294" s="42" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A295" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B295" s="5">
@@ -7357,10 +8281,13 @@
       <c r="D295" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E295" s="45"/>
-    </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A296" s="40" t="s">
+      <c r="E295" s="42"/>
+      <c r="F295" s="42" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A296" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B296" s="5">
@@ -7373,9 +8300,12 @@
         <v>100</v>
       </c>
       <c r="E296" s="17"/>
-    </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A297" s="40" t="s">
+      <c r="F296" s="17" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A297" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B297" s="5">
@@ -7387,10 +8317,13 @@
       <c r="D297" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E297" s="45"/>
-    </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A298" s="40" t="s">
+      <c r="E297" s="42"/>
+      <c r="F297" s="42" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A298" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B298" s="5">
@@ -7402,10 +8335,13 @@
       <c r="D298" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E298" s="45"/>
-    </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A299" s="40" t="s">
+      <c r="E298" s="42"/>
+      <c r="F298" s="42" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A299" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B299" s="5">
@@ -7417,10 +8353,13 @@
       <c r="D299" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E299" s="45"/>
-    </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A300" s="40" t="s">
+      <c r="E299" s="42"/>
+      <c r="F299" s="42" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A300" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B300" s="5">
@@ -7432,10 +8371,13 @@
       <c r="D300" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E300" s="45"/>
-    </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A301" s="40" t="s">
+      <c r="E300" s="42"/>
+      <c r="F300" s="42" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A301" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B301" s="5">
@@ -7448,9 +8390,12 @@
         <v>100</v>
       </c>
       <c r="E301" s="17"/>
-    </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A302" s="40" t="s">
+      <c r="F301" s="17" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A302" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B302" s="5">
@@ -7462,10 +8407,13 @@
       <c r="D302" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E302" s="19"/>
-    </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A303" s="40" t="s">
+      <c r="E302" s="18"/>
+      <c r="F302" s="18" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A303" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B303" s="5">
@@ -7477,10 +8425,13 @@
       <c r="D303" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="E303" s="45"/>
-    </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A304" s="40" t="s">
+      <c r="E303" s="42"/>
+      <c r="F303" s="42" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A304" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B304" s="5">
@@ -7493,9 +8444,12 @@
         <v>100</v>
       </c>
       <c r="E304" s="17"/>
-    </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A305" s="40" t="s">
+      <c r="F304" s="17" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A305" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B305" s="5">
@@ -7508,9 +8462,12 @@
         <v>100</v>
       </c>
       <c r="E305" s="17"/>
-    </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A306" s="40" t="s">
+      <c r="F305" s="17" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A306" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B306" s="5">
@@ -7522,10 +8479,13 @@
       <c r="D306" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E306" s="45"/>
-    </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A307" s="40" t="s">
+      <c r="E306" s="42"/>
+      <c r="F306" s="42" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A307" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B307" s="5">
@@ -7537,10 +8497,13 @@
       <c r="D307" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E307" s="45"/>
-    </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A308" s="40" t="s">
+      <c r="E307" s="42"/>
+      <c r="F307" s="42" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A308" s="37" t="s">
         <v>274</v>
       </c>
       <c r="B308" s="5">
@@ -7552,37 +8515,51 @@
       <c r="D308" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E308" s="45"/>
-    </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A309" s="46" t="s">
-        <v>274</v>
-      </c>
-      <c r="B309" s="47">
+      <c r="E308" s="42"/>
+      <c r="F308" s="42" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A309" s="43" t="s">
+        <v>274</v>
+      </c>
+      <c r="B309" s="44">
         <v>132</v>
       </c>
-      <c r="C309" s="48" t="s">
+      <c r="C309" s="45" t="s">
         <v>417</v>
       </c>
-      <c r="D309" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="E309" s="45"/>
-    </row>
-    <row r="310" spans="1:5" ht="102" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A310" s="50" t="s">
-        <v>274</v>
-      </c>
-      <c r="B310" s="51">
+      <c r="D309" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="E309" s="42"/>
+      <c r="F309" s="42" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" ht="102" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A310" s="47" t="s">
+        <v>274</v>
+      </c>
+      <c r="B310" s="48">
         <v>133</v>
       </c>
-      <c r="C310" s="52" t="s">
+      <c r="C310" s="49" t="s">
         <v>418</v>
       </c>
-      <c r="D310" s="53" t="s">
+      <c r="D310" s="50" t="s">
         <v>419</v>
       </c>
-      <c r="E310" s="29"/>
+      <c r="E310" s="27"/>
+      <c r="F310" s="27" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F311" s="27" t="s">
+        <v>92</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F310" xr:uid="{00000000-0001-0000-0000-000000000000}">

--- a/ControlTable_Sentry_ARL/ControlTable_SentryARL.xlsx
+++ b/ControlTable_Sentry_ARL/ControlTable_SentryARL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Y26\ControlTable_Sentry_ARL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3311668A-E375-48E2-ADB6-AE27F8110E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B6AB9AB-E266-4511-91DA-55ACD2C03E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1431B911-F057-4304-9798-EC2268DBF203}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{1431B911-F057-4304-9798-EC2268DBF203}"/>
   </bookViews>
   <sheets>
     <sheet name="Sentry_ARL_" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="502">
   <si>
     <t>项目</t>
     <phoneticPr fontId="0" type="noConversion"/>
@@ -2245,12 +2245,52 @@
   <si>
     <t>IF @%TECHECK%==@NOTREADY GOTO PASS</t>
   </si>
+  <si>
+    <t>test 100% 
+:PASS
+ISSU.exe -pdt -setpdt SentryNV14Rpl_PDT_2in1_20230914.bin</t>
+  </si>
+  <si>
+    <t>chỉ test bàn phím 80%, sau này có model 16in ko ?
+Chưa xóa PJ hàng khác trong chương trình</t>
+  </si>
+  <si>
+    <t>close__only 1 port type</t>
+  </si>
+  <si>
+    <t>not add change it</t>
+  </si>
+  <si>
+    <t>not test</t>
+  </si>
+  <si>
+    <t>not need item</t>
+  </si>
+  <si>
+    <t>close TO_Update.bat</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">WCD: Goodix test
+WVN: not test </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Goodix</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2382,6 +2422,13 @@
       <color rgb="FF92D050"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="10">
@@ -2569,7 +2616,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2730,13 +2777,14 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3101,12 +3149,12 @@
       <c r="E1" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="F1" s="58" t="s">
+      <c r="F1" s="57" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="59" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="5">
@@ -3120,7 +3168,7 @@
       <c r="E2" s="8"/>
     </row>
     <row r="3" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="56"/>
+      <c r="A3" s="59"/>
       <c r="B3" s="5">
         <f t="shared" ref="B3:B13" si="0">ROW()-1</f>
         <v>2</v>
@@ -3132,7 +3180,7 @@
       <c r="E3" s="8"/>
     </row>
     <row r="4" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="56"/>
+      <c r="A4" s="59"/>
       <c r="B4" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -3144,7 +3192,7 @@
       <c r="E4" s="8"/>
     </row>
     <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="56"/>
+      <c r="A5" s="59"/>
       <c r="B5" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -3158,7 +3206,7 @@
       <c r="E5" s="8"/>
     </row>
     <row r="6" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="56"/>
+      <c r="A6" s="59"/>
       <c r="B6" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -3172,7 +3220,7 @@
       <c r="E6" s="8"/>
     </row>
     <row r="7" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="56" t="s">
+      <c r="A7" s="59" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="5">
@@ -3188,7 +3236,7 @@
       <c r="E7" s="8"/>
     </row>
     <row r="8" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="56"/>
+      <c r="A8" s="59"/>
       <c r="B8" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -3202,7 +3250,7 @@
       <c r="E8" s="8"/>
     </row>
     <row r="9" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="56"/>
+      <c r="A9" s="59"/>
       <c r="B9" s="5">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -3216,7 +3264,7 @@
       <c r="E9" s="8"/>
     </row>
     <row r="10" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="56"/>
+      <c r="A10" s="59"/>
       <c r="B10" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -3230,7 +3278,7 @@
       <c r="E10" s="8"/>
     </row>
     <row r="11" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="56"/>
+      <c r="A11" s="59"/>
       <c r="B11" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -3244,7 +3292,7 @@
       <c r="E11" s="8"/>
     </row>
     <row r="12" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="56"/>
+      <c r="A12" s="59"/>
       <c r="B12" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -3258,7 +3306,7 @@
       <c r="E12" s="8"/>
     </row>
     <row r="13" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="56"/>
+      <c r="A13" s="59"/>
       <c r="B13" s="5">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -4075,7 +4123,7 @@
       <c r="E62" s="9" t="s">
         <v>426</v>
       </c>
-      <c r="F62" s="57" t="s">
+      <c r="F62" s="56" t="s">
         <v>443</v>
       </c>
     </row>
@@ -4742,7 +4790,9 @@
       <c r="D97" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="E97" s="13"/>
+      <c r="E97" s="13" t="s">
+        <v>172</v>
+      </c>
       <c r="F97" s="13" t="s">
         <v>172</v>
       </c>
@@ -4763,7 +4813,9 @@
       <c r="D98" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="E98" s="26"/>
+      <c r="E98" s="26" t="s">
+        <v>452</v>
+      </c>
       <c r="F98" s="26" t="s">
         <v>452</v>
       </c>
@@ -4781,7 +4833,9 @@
       <c r="D99" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E99" s="26"/>
+      <c r="E99" s="26" t="s">
+        <v>452</v>
+      </c>
       <c r="F99" s="26" t="s">
         <v>452</v>
       </c>
@@ -4799,7 +4853,9 @@
       <c r="D100" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="E100" s="27"/>
+      <c r="E100" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F100" s="27" t="s">
         <v>172</v>
       </c>
@@ -4817,7 +4873,9 @@
       <c r="D101" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E101" s="27"/>
+      <c r="E101" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F101" s="27" t="s">
         <v>172</v>
       </c>
@@ -4835,7 +4893,9 @@
       <c r="D102" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E102" s="26"/>
+      <c r="E102" s="26" t="s">
+        <v>431</v>
+      </c>
       <c r="F102" s="26" t="s">
         <v>452</v>
       </c>
@@ -4853,7 +4913,9 @@
       <c r="D103" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E103" s="27"/>
+      <c r="E103" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F103" s="27" t="s">
         <v>172</v>
       </c>
@@ -4871,7 +4933,9 @@
       <c r="D104" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E104" s="27"/>
+      <c r="E104" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F104" s="27" t="s">
         <v>172</v>
       </c>
@@ -4889,7 +4953,9 @@
       <c r="D105" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E105" s="27"/>
+      <c r="E105" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F105" s="27" t="s">
         <v>172</v>
       </c>
@@ -4907,7 +4973,9 @@
       <c r="D106" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E106" s="27"/>
+      <c r="E106" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F106" s="27" t="s">
         <v>172</v>
       </c>
@@ -4925,7 +4993,9 @@
       <c r="D107" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E107" s="27"/>
+      <c r="E107" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F107" s="27"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.35">
@@ -4941,7 +5011,9 @@
       <c r="D108" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E108" s="27"/>
+      <c r="E108" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F108" s="27" t="s">
         <v>172</v>
       </c>
@@ -4959,7 +5031,9 @@
       <c r="D109" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="E109" s="17"/>
+      <c r="E109" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F109" s="17" t="s">
         <v>453</v>
       </c>
@@ -4977,7 +5051,9 @@
       <c r="D110" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="E110" s="13"/>
+      <c r="E110" s="18" t="s">
+        <v>494</v>
+      </c>
       <c r="F110" s="13" t="s">
         <v>454</v>
       </c>
@@ -4995,7 +5071,9 @@
       <c r="D111" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E111" s="13"/>
+      <c r="E111" s="13" t="s">
+        <v>431</v>
+      </c>
       <c r="F111" s="13" t="s">
         <v>431</v>
       </c>
@@ -5013,7 +5091,9 @@
       <c r="D112" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E112" s="17"/>
+      <c r="E112" s="17" t="s">
+        <v>453</v>
+      </c>
       <c r="F112" s="17" t="s">
         <v>453</v>
       </c>
@@ -5031,7 +5111,9 @@
       <c r="D113" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E113" s="17"/>
+      <c r="E113" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F113" s="17" t="s">
         <v>453</v>
       </c>
@@ -5049,7 +5131,9 @@
       <c r="D114" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E114" s="27"/>
+      <c r="E114" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F114" s="27" t="s">
         <v>172</v>
       </c>
@@ -5067,7 +5151,9 @@
       <c r="D115" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="E115" s="17"/>
+      <c r="E115" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F115" s="17" t="s">
         <v>453</v>
       </c>
@@ -5085,7 +5171,9 @@
       <c r="D116" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E116" s="13"/>
+      <c r="E116" s="13" t="s">
+        <v>172</v>
+      </c>
       <c r="F116" s="13"/>
     </row>
     <row r="117" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
@@ -5101,7 +5189,9 @@
       <c r="D117" s="28" t="s">
         <v>199</v>
       </c>
-      <c r="E117" s="27"/>
+      <c r="E117" s="18" t="s">
+        <v>495</v>
+      </c>
       <c r="F117" s="27" t="s">
         <v>455</v>
       </c>
@@ -5119,7 +5209,9 @@
       <c r="D118" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E118" s="27"/>
+      <c r="E118" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F118" s="27" t="s">
         <v>456</v>
       </c>
@@ -5137,7 +5229,9 @@
       <c r="D119" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E119" s="27"/>
+      <c r="E119" s="27" t="s">
+        <v>92</v>
+      </c>
       <c r="F119" s="27" t="s">
         <v>456</v>
       </c>
@@ -5155,7 +5249,9 @@
       <c r="D120" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E120" s="18"/>
+      <c r="E120" s="27" t="s">
+        <v>92</v>
+      </c>
       <c r="F120" s="18" t="s">
         <v>457</v>
       </c>
@@ -5173,7 +5269,9 @@
       <c r="D121" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E121" s="18"/>
+      <c r="E121" s="27" t="s">
+        <v>92</v>
+      </c>
       <c r="F121" s="18" t="s">
         <v>457</v>
       </c>
@@ -5191,7 +5289,9 @@
       <c r="D122" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E122" s="27"/>
+      <c r="E122" s="27" t="s">
+        <v>92</v>
+      </c>
       <c r="F122" s="27" t="s">
         <v>456</v>
       </c>
@@ -5209,7 +5309,9 @@
       <c r="D123" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E123" s="27"/>
+      <c r="E123" s="27" t="s">
+        <v>92</v>
+      </c>
       <c r="F123" s="27" t="s">
         <v>456</v>
       </c>
@@ -5227,7 +5329,9 @@
       <c r="D124" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E124" s="27"/>
+      <c r="E124" s="27" t="s">
+        <v>496</v>
+      </c>
       <c r="F124" s="27" t="s">
         <v>456</v>
       </c>
@@ -5245,7 +5349,9 @@
       <c r="D125" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="E125" s="18"/>
+      <c r="E125" s="18" t="s">
+        <v>497</v>
+      </c>
       <c r="F125" s="18" t="s">
         <v>457</v>
       </c>
@@ -5263,7 +5369,9 @@
       <c r="D126" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E126" s="27"/>
+      <c r="E126" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F126" s="27" t="s">
         <v>456</v>
       </c>
@@ -5281,7 +5389,9 @@
       <c r="D127" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E127" s="18"/>
+      <c r="E127" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F127" s="18" t="s">
         <v>457</v>
       </c>
@@ -5299,7 +5409,9 @@
       <c r="D128" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E128" s="27"/>
+      <c r="E128" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F128" s="27" t="s">
         <v>456</v>
       </c>
@@ -5317,7 +5429,9 @@
       <c r="D129" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E129" s="27"/>
+      <c r="E129" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F129" s="27" t="s">
         <v>456</v>
       </c>
@@ -5335,7 +5449,9 @@
       <c r="D130" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E130" s="18"/>
+      <c r="E130" s="18" t="s">
+        <v>423</v>
+      </c>
       <c r="F130" s="18" t="s">
         <v>457</v>
       </c>
@@ -5353,7 +5469,9 @@
       <c r="D131" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E131" s="18"/>
+      <c r="E131" s="18" t="s">
+        <v>423</v>
+      </c>
       <c r="F131" s="18" t="s">
         <v>457</v>
       </c>
@@ -5371,7 +5489,9 @@
       <c r="D132" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E132" s="29"/>
+      <c r="E132" s="29" t="s">
+        <v>172</v>
+      </c>
       <c r="F132" s="29" t="s">
         <v>456</v>
       </c>
@@ -5389,7 +5509,9 @@
       <c r="D133" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E133" s="18"/>
+      <c r="E133" s="18" t="s">
+        <v>423</v>
+      </c>
       <c r="F133" s="18" t="s">
         <v>457</v>
       </c>
@@ -5407,7 +5529,9 @@
       <c r="D134" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E134" s="18"/>
+      <c r="E134" s="18" t="s">
+        <v>423</v>
+      </c>
       <c r="F134" s="18" t="s">
         <v>457</v>
       </c>
@@ -5425,7 +5549,9 @@
       <c r="D135" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E135" s="13"/>
+      <c r="E135" s="13" t="s">
+        <v>172</v>
+      </c>
       <c r="F135" s="13" t="s">
         <v>456</v>
       </c>
@@ -5443,7 +5569,9 @@
       <c r="D136" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E136" s="27"/>
+      <c r="E136" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F136" s="27" t="s">
         <v>172</v>
       </c>
@@ -5461,7 +5589,9 @@
       <c r="D137" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E137" s="30"/>
+      <c r="E137" s="30" t="s">
+        <v>172</v>
+      </c>
       <c r="F137" s="30" t="s">
         <v>458</v>
       </c>
@@ -5479,7 +5609,9 @@
       <c r="D138" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E138" s="27"/>
+      <c r="E138" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F138" s="27" t="s">
         <v>172</v>
       </c>
@@ -5497,7 +5629,9 @@
       <c r="D139" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E139" s="27"/>
+      <c r="E139" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F139" s="27" t="s">
         <v>172</v>
       </c>
@@ -5515,7 +5649,9 @@
       <c r="D140" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E140" s="27"/>
+      <c r="E140" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F140" s="27" t="s">
         <v>172</v>
       </c>
@@ -5533,7 +5669,9 @@
       <c r="D141" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E141" s="27"/>
+      <c r="E141" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F141" s="27" t="s">
         <v>172</v>
       </c>
@@ -5551,7 +5689,9 @@
       <c r="D142" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E142" s="31"/>
+      <c r="E142" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F142" s="31" t="s">
         <v>459</v>
       </c>
@@ -5569,7 +5709,9 @@
       <c r="D143" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="E143" s="27"/>
+      <c r="E143" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F143" s="27" t="s">
         <v>172</v>
       </c>
@@ -5587,7 +5729,9 @@
       <c r="D144" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="E144" s="18"/>
+      <c r="E144" s="18" t="s">
+        <v>423</v>
+      </c>
       <c r="F144" s="18" t="s">
         <v>457</v>
       </c>
@@ -5605,7 +5749,9 @@
       <c r="D145" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E145" s="18"/>
+      <c r="E145" s="18" t="s">
+        <v>423</v>
+      </c>
       <c r="F145" s="18" t="s">
         <v>457</v>
       </c>
@@ -5623,7 +5769,9 @@
       <c r="D146" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E146" s="18"/>
+      <c r="E146" s="18" t="s">
+        <v>423</v>
+      </c>
       <c r="F146" s="18" t="s">
         <v>457</v>
       </c>
@@ -5641,7 +5789,9 @@
       <c r="D147" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E147" s="27"/>
+      <c r="E147" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F147" s="27" t="s">
         <v>172</v>
       </c>
@@ -5677,7 +5827,9 @@
       <c r="D149" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="E149" s="12"/>
+      <c r="E149" s="12" t="s">
+        <v>172</v>
+      </c>
       <c r="F149" s="12" t="s">
         <v>92</v>
       </c>
@@ -5695,7 +5847,9 @@
       <c r="D150" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E150" s="12"/>
+      <c r="E150" s="12" t="s">
+        <v>172</v>
+      </c>
       <c r="F150" s="12" t="s">
         <v>92</v>
       </c>
@@ -5713,7 +5867,9 @@
       <c r="D151" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="E151" s="12"/>
+      <c r="E151" s="12" t="s">
+        <v>172</v>
+      </c>
       <c r="F151" s="12" t="s">
         <v>92</v>
       </c>
@@ -5731,7 +5887,9 @@
       <c r="D152" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="E152" s="17"/>
+      <c r="E152" s="12" t="s">
+        <v>172</v>
+      </c>
       <c r="F152" s="17" t="s">
         <v>460</v>
       </c>
@@ -5747,7 +5905,9 @@
         <v>238</v>
       </c>
       <c r="D153" s="19"/>
-      <c r="E153" s="27"/>
+      <c r="E153" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F153" s="27" t="s">
         <v>456</v>
       </c>
@@ -5763,7 +5923,9 @@
         <v>239</v>
       </c>
       <c r="D154" s="9"/>
-      <c r="E154" s="27"/>
+      <c r="E154" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F154" s="27" t="s">
         <v>456</v>
       </c>
@@ -5781,7 +5943,9 @@
       <c r="D155" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E155" s="27"/>
+      <c r="E155" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F155" s="27" t="s">
         <v>456</v>
       </c>
@@ -5799,7 +5963,9 @@
       <c r="D156" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E156" s="18"/>
+      <c r="E156" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F156" s="18" t="s">
         <v>461</v>
       </c>
@@ -5817,7 +5983,9 @@
       <c r="D157" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="E157" s="12"/>
+      <c r="E157" s="12" t="s">
+        <v>172</v>
+      </c>
       <c r="F157" s="12" t="s">
         <v>92</v>
       </c>
@@ -5835,7 +6003,9 @@
       <c r="D158" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="E158" s="18"/>
+      <c r="E158" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F158" s="18" t="s">
         <v>462</v>
       </c>
@@ -5853,7 +6023,9 @@
       <c r="D159" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E159" s="27"/>
+      <c r="E159" s="27" t="s">
+        <v>172</v>
+      </c>
       <c r="F159" s="27" t="s">
         <v>456</v>
       </c>
@@ -5871,7 +6043,9 @@
       <c r="D160" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="E160" s="13"/>
+      <c r="E160" s="13" t="s">
+        <v>172</v>
+      </c>
       <c r="F160" s="13" t="s">
         <v>463</v>
       </c>
@@ -5889,7 +6063,9 @@
       <c r="D161" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E161" s="13"/>
+      <c r="E161" s="13" t="s">
+        <v>172</v>
+      </c>
       <c r="F161" s="13" t="s">
         <v>463</v>
       </c>
@@ -5907,7 +6083,9 @@
       <c r="D162" s="33" t="s">
         <v>251</v>
       </c>
-      <c r="E162" s="29"/>
+      <c r="E162" s="29" t="s">
+        <v>172</v>
+      </c>
       <c r="F162" s="29" t="s">
         <v>456</v>
       </c>
@@ -5925,7 +6103,9 @@
       <c r="D163" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E163" s="13"/>
+      <c r="E163" s="13" t="s">
+        <v>172</v>
+      </c>
       <c r="F163" s="13"/>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.35">
@@ -5941,7 +6121,9 @@
       <c r="D164" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E164" s="29"/>
+      <c r="E164" s="29" t="s">
+        <v>172</v>
+      </c>
       <c r="F164" s="29" t="s">
         <v>456</v>
       </c>
@@ -5959,7 +6141,9 @@
       <c r="D165" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="E165" s="34"/>
+      <c r="E165" s="34" t="s">
+        <v>423</v>
+      </c>
       <c r="F165" s="34" t="s">
         <v>453</v>
       </c>
@@ -5977,7 +6161,9 @@
       <c r="D166" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="E166" s="29"/>
+      <c r="E166" s="18" t="s">
+        <v>423</v>
+      </c>
       <c r="F166" s="29" t="s">
         <v>456</v>
       </c>
@@ -5995,7 +6181,9 @@
       <c r="D167" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="E167" s="18"/>
+      <c r="E167" s="18" t="s">
+        <v>423</v>
+      </c>
       <c r="F167" s="18" t="s">
         <v>464</v>
       </c>
@@ -6013,7 +6201,9 @@
       <c r="D168" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E168" s="18"/>
+      <c r="E168" s="29" t="s">
+        <v>172</v>
+      </c>
       <c r="F168" s="18" t="s">
         <v>465</v>
       </c>
@@ -6031,7 +6221,9 @@
       <c r="D169" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="E169" s="13"/>
+      <c r="E169" s="18" t="s">
+        <v>453</v>
+      </c>
       <c r="F169" s="13" t="s">
         <v>453</v>
       </c>
@@ -6049,7 +6241,9 @@
       <c r="D170" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="E170" s="18"/>
+      <c r="E170" s="18" t="s">
+        <v>453</v>
+      </c>
       <c r="F170" s="18" t="s">
         <v>466</v>
       </c>
@@ -6067,7 +6261,9 @@
       <c r="D171" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="E171" s="29"/>
+      <c r="E171" s="29" t="s">
+        <v>172</v>
+      </c>
       <c r="F171" s="29" t="s">
         <v>456</v>
       </c>
@@ -6085,7 +6281,9 @@
       <c r="D172" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E172" s="18"/>
+      <c r="E172" s="29" t="s">
+        <v>172</v>
+      </c>
       <c r="F172" s="18" t="s">
         <v>453</v>
       </c>
@@ -6103,7 +6301,9 @@
       <c r="D173" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E173" s="18"/>
+      <c r="E173" s="29" t="s">
+        <v>172</v>
+      </c>
       <c r="F173" s="18" t="s">
         <v>453</v>
       </c>
@@ -6121,7 +6321,9 @@
       <c r="D174" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E174" s="18"/>
+      <c r="E174" s="18" t="s">
+        <v>499</v>
+      </c>
       <c r="F174" s="18" t="s">
         <v>457</v>
       </c>
@@ -6139,7 +6341,9 @@
       <c r="D175" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E175" s="18"/>
+      <c r="E175" s="18" t="s">
+        <v>498</v>
+      </c>
       <c r="F175" s="18" t="s">
         <v>457</v>
       </c>
@@ -6157,7 +6361,9 @@
       <c r="D176" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E176" s="18"/>
+      <c r="E176" s="18" t="s">
+        <v>498</v>
+      </c>
       <c r="F176" s="18" t="s">
         <v>457</v>
       </c>
@@ -6175,7 +6381,9 @@
       <c r="D177" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="E177" s="27"/>
+      <c r="E177" s="18" t="s">
+        <v>498</v>
+      </c>
       <c r="F177" s="27" t="s">
         <v>454</v>
       </c>
@@ -6193,7 +6401,9 @@
       <c r="D178" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E178" s="29"/>
+      <c r="E178" s="29" t="s">
+        <v>172</v>
+      </c>
       <c r="F178" s="29" t="s">
         <v>456</v>
       </c>
@@ -6211,7 +6421,9 @@
       <c r="D179" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E179" s="18"/>
+      <c r="E179" s="18" t="s">
+        <v>452</v>
+      </c>
       <c r="F179" s="18" t="s">
         <v>452</v>
       </c>
@@ -6227,7 +6439,9 @@
         <v>180</v>
       </c>
       <c r="D180" s="9"/>
-      <c r="E180" s="18"/>
+      <c r="E180" s="18" t="s">
+        <v>452</v>
+      </c>
       <c r="F180" s="18" t="s">
         <v>452</v>
       </c>
@@ -6245,7 +6459,9 @@
       <c r="D181" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E181" s="18"/>
+      <c r="E181" s="18" t="s">
+        <v>452</v>
+      </c>
       <c r="F181" s="18" t="s">
         <v>452</v>
       </c>
@@ -6263,7 +6479,9 @@
       <c r="D182" s="38" t="s">
         <v>278</v>
       </c>
-      <c r="E182" s="18"/>
+      <c r="E182" s="29" t="s">
+        <v>172</v>
+      </c>
       <c r="F182" s="18" t="s">
         <v>467</v>
       </c>
@@ -6281,7 +6499,9 @@
       <c r="D183" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E183" s="18"/>
+      <c r="E183" s="18" t="s">
+        <v>452</v>
+      </c>
       <c r="F183" s="18" t="s">
         <v>452</v>
       </c>
@@ -6299,7 +6519,9 @@
       <c r="D184" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="E184" s="29"/>
+      <c r="E184" s="29" t="s">
+        <v>172</v>
+      </c>
       <c r="F184" s="29" t="s">
         <v>456</v>
       </c>
@@ -6317,7 +6539,9 @@
       <c r="D185" s="19" t="s">
         <v>281</v>
       </c>
-      <c r="E185" s="29"/>
+      <c r="E185" s="41" t="s">
+        <v>423</v>
+      </c>
       <c r="F185" s="29" t="s">
         <v>456</v>
       </c>
@@ -6335,7 +6559,9 @@
       <c r="D186" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E186" s="18"/>
+      <c r="E186" s="58" t="s">
+        <v>500</v>
+      </c>
       <c r="F186" s="18" t="s">
         <v>468</v>
       </c>
@@ -6353,7 +6579,9 @@
       <c r="D187" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E187" s="13"/>
+      <c r="E187" s="13" t="s">
+        <v>429</v>
+      </c>
       <c r="F187" s="13"/>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.35">
@@ -6367,7 +6595,9 @@
         <v>284</v>
       </c>
       <c r="D188" s="9"/>
-      <c r="E188" s="13"/>
+      <c r="E188" s="13" t="s">
+        <v>172</v>
+      </c>
       <c r="F188" s="13"/>
     </row>
     <row r="189" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
@@ -6383,7 +6613,9 @@
       <c r="D189" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="E189" s="29"/>
+      <c r="E189" s="41" t="s">
+        <v>501</v>
+      </c>
       <c r="F189" s="29" t="s">
         <v>469</v>
       </c>
@@ -6401,7 +6633,9 @@
       <c r="D190" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="E190" s="40"/>
+      <c r="E190" s="40" t="s">
+        <v>172</v>
+      </c>
       <c r="F190" s="40" t="s">
         <v>456</v>
       </c>
@@ -6541,7 +6775,9 @@
       <c r="D198" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="E198" s="18"/>
+      <c r="E198" s="18" t="s">
+        <v>453</v>
+      </c>
       <c r="F198" s="18" t="s">
         <v>453</v>
       </c>
@@ -8589,6 +8825,14 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="4f11c476-4dff-4b38-bd86-40c4011cf4e3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007F4AA25A4831004A8CF7B223D5296C3B" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="88b1a828e38bf51fd90d073f532db327">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="4f11c476-4dff-4b38-bd86-40c4011cf4e3" xmlns:ns4="9ec5a528-7697-40f0-ab57-0efe8d7498af" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dd8c64aa141013cabd5fe7e29ee99071" ns3:_="" ns4:_="">
     <xsd:import namespace="4f11c476-4dff-4b38-bd86-40c4011cf4e3"/>
@@ -8815,14 +9059,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="4f11c476-4dff-4b38-bd86-40c4011cf4e3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40E1FBC7-4132-47AD-BE69-00EBA3F0A061}">
   <ds:schemaRefs>
@@ -8832,6 +9068,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D18A90A6-8D26-4049-A3C5-C8F9942C3FA2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="9ec5a528-7697-40f0-ab57-0efe8d7498af"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="4f11c476-4dff-4b38-bd86-40c4011cf4e3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B8E655D-77CA-42D5-BD57-CDF96A11FD6C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8848,21 +9101,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D18A90A6-8D26-4049-A3C5-C8F9942C3FA2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="9ec5a528-7697-40f0-ab57-0efe8d7498af"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="4f11c476-4dff-4b38-bd86-40c4011cf4e3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>